--- a/Techniques/Univariate Statistical Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_univariate/univariate/dsas_g11_univariate_output2.xlsx
+++ b/Techniques/Univariate Statistical Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_univariate/univariate/dsas_g11_univariate_output2.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -430,15 +430,30 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Baseline_Limit(3Sigma)</t>
+          <t>UCL</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Average_Slope_per_Hour</t>
+          <t>LCL</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
+        <is>
+          <t>Avg_Slope_per_Hour</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Target_Limit</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Hours_to_Threshold</t>
         </is>
@@ -451,16 +466,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C2" t="n">
-        <v>48.7254</v>
+        <v>61.0097</v>
       </c>
       <c r="D2" t="n">
-        <v>0.013606</v>
+        <v>46.5288</v>
       </c>
       <c r="E2" t="n">
-        <v>1155.73</v>
+        <v>-0.010275</v>
+      </c>
+      <c r="F2" t="n">
+        <v>46.5288</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Decreasing to LCL</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>435.17</v>
       </c>
     </row>
     <row r="3">
@@ -470,16 +496,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>47.2324</v>
+        <v>84.0108</v>
       </c>
       <c r="D3" t="n">
-        <v>0.016239</v>
+        <v>67.264</v>
       </c>
       <c r="E3" t="n">
-        <v>568.53</v>
+        <v>0.084546</v>
+      </c>
+      <c r="F3" t="n">
+        <v>84.0108</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Increasing to UCL</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>142.06</v>
       </c>
     </row>
     <row r="4">
@@ -489,16 +526,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C4" t="n">
-        <v>35.6108</v>
+        <v>48.3419</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001281</v>
+        <v>29.5152</v>
       </c>
       <c r="E4" t="n">
-        <v>2819.77</v>
+        <v>-0.013333</v>
+      </c>
+      <c r="F4" t="n">
+        <v>29.5152</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Decreasing to LCL</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>561.39</v>
       </c>
     </row>
     <row r="5">
@@ -508,16 +556,27 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C5" t="n">
-        <v>60.5885</v>
+        <v>87.41589999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.011599</v>
+        <v>69.32040000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>50.74</v>
+        <v>-0.039136</v>
+      </c>
+      <c r="F5" t="n">
+        <v>69.32040000000001</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Decreasing to LCL</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>17.37</v>
       </c>
     </row>
   </sheetData>
@@ -549,121 +608,121 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AssetID_12208</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.5911</v>
+        <v>3.1699</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AssetID_9368</t>
+          <t>AssetID_9361</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7092000000000001</v>
+        <v>2.2097</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AssetID_9343</t>
+          <t>AssetID_9344</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6958</v>
+        <v>1.671</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>AssetID_9358</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5632</v>
+        <v>1.3584</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AssetID_9369</t>
+          <t>AssetID_9359</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4215</v>
+        <v>1.2655</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AssetID_9361</t>
+          <t>AssetID_9357</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3898</v>
+        <v>1.2307</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AssetID_9344</t>
+          <t>AssetID_9360</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3275</v>
+        <v>1.1933</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AssetID_9360</t>
+          <t>AssetID_9370</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2667</v>
+        <v>1.0233</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AssetID_9358</t>
+          <t>AssetID_9369</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2352</v>
+        <v>0.5649</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AssetID_9408</t>
+          <t>AssetID_9368</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1658</v>
+        <v>0.5491</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AssetID_9359</t>
+          <t>AssetID_9343</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.5433</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AssetID_9370</t>
+          <t>AssetID_9408</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.2238</v>
       </c>
     </row>
   </sheetData>

--- a/Techniques/Univariate Statistical Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_univariate/univariate/dsas_g11_univariate_output2.xlsx
+++ b/Techniques/Univariate Statistical Monitoring/outputs/G11/dsas_g11_bearings_vibration_temp_univariate/univariate/dsas_g11_univariate_output2.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Speed_Analysis" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="RCA_Ranking" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Speed_Analysis" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RCA_Ranking" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,48 +427,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sensor</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Current_Value</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Current_Raw_Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Current_EWMA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>UCL</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>LCL</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Avg_Slope_per_Hour</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Target_Limit</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Hours_to_Threshold</t>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline_Mean</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline_Std</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Average_Slope_per_Hour</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Hours_to_UCL</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Out_Of_Control</t>
         </is>
       </c>
     </row>
@@ -469,24 +492,30 @@
         <v>51</v>
       </c>
       <c r="C2" t="n">
-        <v>61.0097</v>
+        <v>45.7467</v>
       </c>
       <c r="D2" t="n">
-        <v>46.5288</v>
+        <v>56.1827</v>
       </c>
       <c r="E2" t="n">
+        <v>51.3557</v>
+      </c>
+      <c r="F2" t="n">
+        <v>53.7692</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.4135</v>
+      </c>
+      <c r="H2" t="n">
         <v>-0.010275</v>
       </c>
-      <c r="F2" t="n">
-        <v>46.5288</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Decreasing to LCL</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>435.17</v>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Yes ⚠️</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -499,24 +528,30 @@
         <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>84.0108</v>
+        <v>68.5026</v>
       </c>
       <c r="D3" t="n">
-        <v>67.264</v>
+        <v>78.4285</v>
       </c>
       <c r="E3" t="n">
+        <v>72.8462</v>
+      </c>
+      <c r="F3" t="n">
+        <v>75.6374</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.7911</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.084546</v>
       </c>
-      <c r="F3" t="n">
-        <v>84.0108</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Increasing to UCL</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>142.06</v>
+      <c r="I3" t="n">
+        <v>76.04000000000001</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Yes ⚠️</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -529,24 +564,30 @@
         <v>37</v>
       </c>
       <c r="C4" t="n">
-        <v>48.3419</v>
+        <v>35.1405</v>
       </c>
       <c r="D4" t="n">
-        <v>29.5152</v>
+        <v>42.0664</v>
       </c>
       <c r="E4" t="n">
+        <v>35.7908</v>
+      </c>
+      <c r="F4" t="n">
+        <v>38.9286</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.1378</v>
+      </c>
+      <c r="H4" t="n">
         <v>-0.013333</v>
       </c>
-      <c r="F4" t="n">
-        <v>29.5152</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Decreasing to LCL</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>561.39</v>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Yes ⚠️</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -559,24 +600,30 @@
         <v>70</v>
       </c>
       <c r="C5" t="n">
-        <v>87.41589999999999</v>
+        <v>68.54770000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>69.32040000000001</v>
+        <v>81.3841</v>
       </c>
       <c r="E5" t="n">
+        <v>75.3522</v>
+      </c>
+      <c r="F5" t="n">
+        <v>78.3681</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.0159</v>
+      </c>
+      <c r="H5" t="n">
         <v>-0.039136</v>
       </c>
-      <c r="F5" t="n">
-        <v>69.32040000000001</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Decreasing to LCL</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>17.37</v>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Yes ⚠️</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -590,16 +637,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sensor</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline_Mean</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Fault_Mean</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Deviation_Score</t>
         </is>
@@ -612,6 +669,12 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>11509.5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>11676.5</v>
+      </c>
+      <c r="D2" t="n">
         <v>3.1699</v>
       </c>
     </row>
@@ -622,6 +685,12 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>78.3681</v>
+      </c>
+      <c r="C3" t="n">
+        <v>71.7039</v>
+      </c>
+      <c r="D3" t="n">
         <v>2.2097</v>
       </c>
     </row>
@@ -632,6 +701,12 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>1.6308</v>
+      </c>
+      <c r="C4" t="n">
+        <v>13.5066</v>
+      </c>
+      <c r="D4" t="n">
         <v>1.671</v>
       </c>
     </row>
@@ -642,6 +717,12 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>53.7692</v>
+      </c>
+      <c r="C5" t="n">
+        <v>50.4908</v>
+      </c>
+      <c r="D5" t="n">
         <v>1.3584</v>
       </c>
     </row>
@@ -652,6 +733,12 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>75.6374</v>
+      </c>
+      <c r="C6" t="n">
+        <v>72.1053</v>
+      </c>
+      <c r="D6" t="n">
         <v>1.2655</v>
       </c>
     </row>
@@ -662,6 +749,12 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>16.9725</v>
+      </c>
+      <c r="C7" t="n">
+        <v>21.9671</v>
+      </c>
+      <c r="D7" t="n">
         <v>1.2307</v>
       </c>
     </row>
@@ -672,6 +765,12 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>38.9286</v>
+      </c>
+      <c r="C8" t="n">
+        <v>35.1842</v>
+      </c>
+      <c r="D8" t="n">
         <v>1.1933</v>
       </c>
     </row>
@@ -682,6 +781,12 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>73.02200000000001</v>
+      </c>
+      <c r="C9" t="n">
+        <v>72.50660000000001</v>
+      </c>
+      <c r="D9" t="n">
         <v>1.0233</v>
       </c>
     </row>
@@ -692,6 +797,12 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>70.42310000000001</v>
+      </c>
+      <c r="C10" t="n">
+        <v>70.8224</v>
+      </c>
+      <c r="D10" t="n">
         <v>0.5649</v>
       </c>
     </row>
@@ -702,6 +813,12 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>74.8956</v>
+      </c>
+      <c r="C11" t="n">
+        <v>75.27630000000001</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.5491</v>
       </c>
     </row>
@@ -712,6 +829,12 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>98.3571</v>
+      </c>
+      <c r="C12" t="n">
+        <v>94.7632</v>
+      </c>
+      <c r="D12" t="n">
         <v>0.5433</v>
       </c>
     </row>
@@ -722,7 +845,99 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>6.3626</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5.8941</v>
+      </c>
+      <c r="D13" t="n">
         <v>0.2238</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Lambda (λ)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UCL Formula</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>μ + 3σ√(λ/(2-λ))</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LCL Formula</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>μ - 3σ√(λ/(2-λ))</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EWMA Formula</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>E_t = λ·X_t + (1-λ)·E_{t-1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Hours_to_UCL Rule</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>If slope&gt;0 and value&lt;UCL → (UCL-value)/slope | Else → 0</t>
+        </is>
       </c>
     </row>
   </sheetData>
